--- a/ci-build/observations-summary.xlsx
+++ b/ci-build/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="119">
   <si>
     <t>Profile</t>
   </si>
@@ -119,22 +119,7 @@
     <t>SNOMED CT#399608002</t>
   </si>
   <si>
-    <t>CS Senologie Follow-Up#nachsorge-art</t>
-  </si>
-  <si>
-    <t>CS Senologie Follow-Up#vitalstatus</t>
-  </si>
-  <si>
     <t>CS Senologie Follow-Up#zweittumor</t>
-  </si>
-  <si>
-    <t>CS Senologie Follow-Up#zweittumor-icd</t>
-  </si>
-  <si>
-    <t>CS Senologie Follow-Up#zweittumor-datum</t>
-  </si>
-  <si>
-    <t>dateTime</t>
   </si>
   <si>
     <t>senologie-genexpressions-score</t>
@@ -517,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -837,28 +822,28 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>18</v>
@@ -872,10 +857,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>13</v>
@@ -884,16 +869,16 @@
         <v>13</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>18</v>
@@ -910,7 +895,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>13</v>
@@ -919,7 +904,7 @@
         <v>13</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>13</v>
@@ -928,7 +913,7 @@
         <v>13</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>18</v>
@@ -945,7 +930,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>13</v>
@@ -954,7 +939,7 @@
         <v>13</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>13</v>
@@ -963,7 +948,7 @@
         <v>13</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>18</v>
@@ -977,28 +962,28 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>42</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>18</v>
@@ -1012,10 +997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>13</v>
@@ -1024,16 +1009,16 @@
         <v>13</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>18</v>
@@ -1047,10 +1032,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>13</v>
@@ -1059,16 +1044,16 @@
         <v>13</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>18</v>
@@ -1082,10 +1067,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>13</v>
@@ -1094,16 +1079,16 @@
         <v>13</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>18</v>
@@ -1120,7 +1105,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>13</v>
@@ -1129,7 +1114,7 @@
         <v>13</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>13</v>
@@ -1138,7 +1123,7 @@
         <v>13</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
@@ -1155,7 +1140,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -1164,7 +1149,7 @@
         <v>13</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>13</v>
@@ -1173,7 +1158,7 @@
         <v>13</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>18</v>
@@ -1187,11 +1172,11 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="B20" t="s" s="2">
-        <v>57</v>
-      </c>
       <c r="C20" t="s" s="2">
         <v>13</v>
       </c>
@@ -1199,13 +1184,13 @@
         <v>13</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>59</v>
@@ -1222,10 +1207,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>13</v>
@@ -1240,10 +1225,10 @@
         <v>13</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>18</v>
@@ -1257,10 +1242,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>13</v>
@@ -1269,16 +1254,16 @@
         <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>18</v>
@@ -1295,7 +1280,7 @@
         <v>13</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>13</v>
@@ -1304,7 +1289,7 @@
         <v>13</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>13</v>
@@ -1313,7 +1298,7 @@
         <v>13</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
@@ -1327,28 +1312,28 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -1365,7 +1350,7 @@
         <v>13</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>13</v>
@@ -1374,7 +1359,7 @@
         <v>13</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>13</v>
@@ -1383,7 +1368,7 @@
         <v>13</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>
@@ -1397,11 +1382,11 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="B26" t="s" s="2">
-        <v>69</v>
-      </c>
       <c r="C26" t="s" s="2">
         <v>13</v>
       </c>
@@ -1409,16 +1394,16 @@
         <v>13</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>18</v>
@@ -1435,7 +1420,7 @@
         <v>13</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>13</v>
@@ -1444,7 +1429,7 @@
         <v>13</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>13</v>
@@ -1453,7 +1438,7 @@
         <v>13</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>18</v>
@@ -1467,28 +1452,28 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>18</v>
@@ -1505,7 +1490,7 @@
         <v>13</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>13</v>
@@ -1514,7 +1499,7 @@
         <v>13</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>13</v>
@@ -1523,7 +1508,7 @@
         <v>13</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>18</v>
@@ -1540,7 +1525,7 @@
         <v>13</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>13</v>
@@ -1549,7 +1534,7 @@
         <v>13</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>13</v>
@@ -1558,7 +1543,7 @@
         <v>13</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>18</v>
@@ -1572,28 +1557,28 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>18</v>
@@ -1610,7 +1595,7 @@
         <v>13</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>13</v>
@@ -1619,7 +1604,7 @@
         <v>13</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>13</v>
@@ -1628,7 +1613,7 @@
         <v>13</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>18</v>
@@ -1645,7 +1630,7 @@
         <v>13</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>13</v>
@@ -1654,7 +1639,7 @@
         <v>13</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>13</v>
@@ -1663,7 +1648,7 @@
         <v>13</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>18</v>
@@ -1680,7 +1665,7 @@
         <v>13</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>13</v>
@@ -1689,7 +1674,7 @@
         <v>13</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>13</v>
@@ -1698,7 +1683,7 @@
         <v>13</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>18</v>
@@ -1712,28 +1697,28 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="D35" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E35" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="F35" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>18</v>
@@ -1750,7 +1735,7 @@
         <v>13</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>13</v>
@@ -1759,7 +1744,7 @@
         <v>13</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>13</v>
@@ -1768,7 +1753,7 @@
         <v>13</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>18</v>
@@ -1785,7 +1770,7 @@
         <v>13</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>13</v>
@@ -1794,7 +1779,7 @@
         <v>13</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>13</v>
@@ -1820,7 +1805,7 @@
         <v>13</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>13</v>
@@ -1829,7 +1814,7 @@
         <v>13</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>13</v>
@@ -1855,7 +1840,7 @@
         <v>13</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>13</v>
@@ -1864,7 +1849,7 @@
         <v>13</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>13</v>
@@ -1890,7 +1875,7 @@
         <v>13</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>13</v>
@@ -1899,7 +1884,7 @@
         <v>13</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>13</v>
@@ -1925,7 +1910,7 @@
         <v>13</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>13</v>
@@ -1934,7 +1919,7 @@
         <v>13</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>13</v>
@@ -1960,7 +1945,7 @@
         <v>13</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>13</v>
@@ -1969,7 +1954,7 @@
         <v>13</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>13</v>
@@ -1995,7 +1980,7 @@
         <v>13</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>13</v>
@@ -2004,16 +1989,16 @@
         <v>13</v>
       </c>
       <c r="E43" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H43" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="F43" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>32</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>18</v>
@@ -2030,7 +2015,7 @@
         <v>13</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>13</v>
@@ -2048,7 +2033,7 @@
         <v>13</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>18</v>
@@ -2065,7 +2050,7 @@
         <v>13</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>13</v>
@@ -2083,7 +2068,7 @@
         <v>13</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>18</v>
@@ -2100,7 +2085,7 @@
         <v>13</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>13</v>
@@ -2135,7 +2120,7 @@
         <v>13</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>13</v>
@@ -2153,7 +2138,7 @@
         <v>13</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>18</v>
@@ -2170,7 +2155,7 @@
         <v>13</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>13</v>
@@ -2179,7 +2164,7 @@
         <v>13</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>13</v>
@@ -2188,7 +2173,7 @@
         <v>13</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>18</v>
@@ -2205,7 +2190,7 @@
         <v>13</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>13</v>
@@ -2214,7 +2199,7 @@
         <v>13</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>13</v>
@@ -2223,7 +2208,7 @@
         <v>13</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>18</v>
@@ -2240,7 +2225,7 @@
         <v>13</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>13</v>
@@ -2249,7 +2234,7 @@
         <v>13</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>13</v>
@@ -2275,7 +2260,7 @@
         <v>13</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>13</v>
@@ -2284,7 +2269,7 @@
         <v>13</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>13</v>
@@ -2293,7 +2278,7 @@
         <v>13</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>18</v>
@@ -2310,7 +2295,7 @@
         <v>13</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>13</v>
@@ -2319,7 +2304,7 @@
         <v>13</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>13</v>
@@ -2328,7 +2313,7 @@
         <v>13</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>18</v>
@@ -2345,7 +2330,7 @@
         <v>13</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>13</v>
@@ -2354,7 +2339,7 @@
         <v>13</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>13</v>
@@ -2380,7 +2365,7 @@
         <v>13</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>13</v>
@@ -2389,7 +2374,7 @@
         <v>13</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>13</v>
@@ -2415,7 +2400,7 @@
         <v>13</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>13</v>
@@ -2424,7 +2409,7 @@
         <v>13</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>13</v>
@@ -2433,7 +2418,7 @@
         <v>13</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>18</v>
@@ -2450,7 +2435,7 @@
         <v>13</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>13</v>
@@ -2459,7 +2444,7 @@
         <v>13</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>13</v>
@@ -2468,7 +2453,7 @@
         <v>13</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>18</v>
@@ -2485,7 +2470,7 @@
         <v>13</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>13</v>
@@ -2494,7 +2479,7 @@
         <v>13</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>13</v>
@@ -2520,7 +2505,7 @@
         <v>13</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>13</v>
@@ -2529,16 +2514,16 @@
         <v>13</v>
       </c>
       <c r="E58" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H58" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="F58" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>32</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>18</v>
@@ -2555,7 +2540,7 @@
         <v>13</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>13</v>
@@ -2590,7 +2575,7 @@
         <v>13</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>13</v>
@@ -2608,7 +2593,7 @@
         <v>13</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>18</v>
@@ -2625,7 +2610,7 @@
         <v>13</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>13</v>
@@ -2643,7 +2628,7 @@
         <v>13</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>18</v>
@@ -2660,7 +2645,7 @@
         <v>13</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>13</v>
@@ -2678,7 +2663,7 @@
         <v>13</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>18</v>
@@ -2695,7 +2680,7 @@
         <v>13</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>13</v>
@@ -2704,7 +2689,7 @@
         <v>13</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>13</v>
@@ -2730,7 +2715,7 @@
         <v>13</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>13</v>
@@ -2739,7 +2724,7 @@
         <v>13</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>13</v>
@@ -2748,7 +2733,7 @@
         <v>13</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>18</v>
@@ -2757,146 +2742,6 @@
         <v>13</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D65" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E65" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="F65" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D66" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E66" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="F66" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D67" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E67" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="F67" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D68" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E68" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="F68" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K68" t="s" s="2">
         <v>13</v>
       </c>
     </row>
